--- a/artfynd/A 2562-2025 artfynd.xlsx
+++ b/artfynd/A 2562-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1057,6 +1057,264 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125657936</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106932</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Storhagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>313501</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6495017</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ett femtontal bladrosetter i ytterslänt på norra sidan vägen.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Åsa Tengström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Åsa Tengström, Anna Ljunggren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125657779</v>
+      </c>
+      <c r="B6" t="n">
+        <v>109082</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storhagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>313513</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6495014</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Enstaka planta i ytterslänt på norra sidan vägen</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Åsa Tengström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Åsa Tengström, Anna Ljunggren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2562-2025 artfynd.xlsx
+++ b/artfynd/A 2562-2025 artfynd.xlsx
@@ -1062,12 +1062,7 @@
         <v>125657936</v>
       </c>
       <c r="B5" t="n">
-        <v>106932</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1195,12 +1190,7 @@
         <v>125657779</v>
       </c>
       <c r="B6" t="n">
-        <v>109082</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109137</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2562-2025 artfynd.xlsx
+++ b/artfynd/A 2562-2025 artfynd.xlsx
@@ -1062,7 +1062,7 @@
         <v>125657936</v>
       </c>
       <c r="B5" t="n">
-        <v>106987</v>
+        <v>106994</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>125657779</v>
       </c>
       <c r="B6" t="n">
-        <v>109137</v>
+        <v>109144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Åsa Tengström, Anna Ljunggren</t>
+          <t>Anna Ljunggren, Åsa Tengström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 2562-2025 artfynd.xlsx
+++ b/artfynd/A 2562-2025 artfynd.xlsx
@@ -1062,7 +1062,7 @@
         <v>125657936</v>
       </c>
       <c r="B5" t="n">
-        <v>106994</v>
+        <v>106997</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>125657779</v>
       </c>
       <c r="B6" t="n">
-        <v>109144</v>
+        <v>109147</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Ljunggren, Åsa Tengström</t>
+          <t>Åsa Tengström, Anna Ljunggren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 2562-2025 artfynd.xlsx
+++ b/artfynd/A 2562-2025 artfynd.xlsx
@@ -1062,7 +1062,7 @@
         <v>125657936</v>
       </c>
       <c r="B5" t="n">
-        <v>106997</v>
+        <v>107001</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>125657779</v>
       </c>
       <c r="B6" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2562-2025 artfynd.xlsx
+++ b/artfynd/A 2562-2025 artfynd.xlsx
@@ -1062,7 +1062,7 @@
         <v>125657936</v>
       </c>
       <c r="B5" t="n">
-        <v>107001</v>
+        <v>107002</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>125657779</v>
       </c>
       <c r="B6" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Åsa Tengström, Anna Ljunggren</t>
+          <t>Anna Ljunggren, Åsa Tengström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 2562-2025 artfynd.xlsx
+++ b/artfynd/A 2562-2025 artfynd.xlsx
@@ -1062,7 +1062,7 @@
         <v>125657936</v>
       </c>
       <c r="B5" t="n">
-        <v>107002</v>
+        <v>107004</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>125657779</v>
       </c>
       <c r="B6" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Ljunggren, Åsa Tengström</t>
+          <t>Åsa Tengström, Anna Ljunggren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 2562-2025 artfynd.xlsx
+++ b/artfynd/A 2562-2025 artfynd.xlsx
@@ -1062,7 +1062,7 @@
         <v>125657936</v>
       </c>
       <c r="B5" t="n">
-        <v>107004</v>
+        <v>107006</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Åsa Tengström, Anna Ljunggren</t>
+          <t>Anna Ljunggren, Åsa Tengström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1190,7 +1190,7 @@
         <v>125657779</v>
       </c>
       <c r="B6" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2562-2025 artfynd.xlsx
+++ b/artfynd/A 2562-2025 artfynd.xlsx
@@ -1062,7 +1062,7 @@
         <v>125657936</v>
       </c>
       <c r="B5" t="n">
-        <v>107006</v>
+        <v>107010</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna Ljunggren, Åsa Tengström</t>
+          <t>Åsa Tengström, Anna Ljunggren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1190,7 +1190,7 @@
         <v>125657779</v>
       </c>
       <c r="B6" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2562-2025 artfynd.xlsx
+++ b/artfynd/A 2562-2025 artfynd.xlsx
@@ -1062,7 +1062,7 @@
         <v>125657936</v>
       </c>
       <c r="B5" t="n">
-        <v>107010</v>
+        <v>107023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>125657779</v>
       </c>
       <c r="B6" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 2562-2025 artfynd.xlsx
+++ b/artfynd/A 2562-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>2361934</v>
       </c>
       <c r="B2" t="n">
-        <v>104837</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>313526.0882228647</v>
+        <v>313526</v>
       </c>
       <c r="R2" t="n">
-        <v>6495029.288108238</v>
+        <v>6495029</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2000-07-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2000-07-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,32 +777,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86493916</v>
+        <v>2361935</v>
       </c>
       <c r="B3" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>219955</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -826,20 +806,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storhagen, Askeslätt, norr väg O934, Boh</t>
+          <t>Askeslätt, 200 m SV om gården, vägkant, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>313504.6455761611</v>
+        <v>313515</v>
       </c>
       <c r="R3" t="n">
-        <v>6495018.815482169</v>
+        <v>6494989</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,24 +840,19 @@
           <t>Hede</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>OB-Mun-0440</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-06-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-07-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-06-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-07-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,34 +861,23 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Norra sidan i ytterslänt</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mats Lindqvist</t>
+          <t>Bohuslän Floraväktarna</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mats Lindqvist, Tobias Federsel</t>
+          <t>Bohuslän Floraväktarna, Eva Falk</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
@@ -926,12 +886,7 @@
         <v>86493913</v>
       </c>
       <c r="B4" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>313504.6455761611</v>
+        <v>313505</v>
       </c>
       <c r="R4" t="n">
-        <v>6495018.815482169</v>
+        <v>6495019</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,19 +955,9 @@
           <t>2020-06-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-06-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1062,7 +1007,7 @@
         <v>125657936</v>
       </c>
       <c r="B5" t="n">
-        <v>107023</v>
+        <v>107908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1187,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125657779</v>
+        <v>86493916</v>
       </c>
       <c r="B6" t="n">
-        <v>109173</v>
+        <v>110078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,17 +1167,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storhagen, Boh</t>
+          <t>Storhagen, Askeslätt, norr väg O934, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>313513</v>
+        <v>313505</v>
       </c>
       <c r="R6" t="n">
-        <v>6495014</v>
+        <v>6495019</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1256,27 +1201,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2020-06-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Enstaka planta i ytterslänt på norra sidan vägen</t>
+          <t>2020-06-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,21 +1215,268 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Norra sidan i ytterslänt</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Mats Lindqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mats Lindqvist, Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>86493935</v>
+      </c>
+      <c r="B7" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Storhagen, Askeslätt, östra sidan väg O934, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>313532</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6495008</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Bankslänt</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mats Lindqvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mats Lindqvist, Tobias Federsel</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125657779</v>
+      </c>
+      <c r="B8" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Storhagen, Boh</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>313513</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6495014</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Munkedal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hede</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Enstaka planta i ytterslänt på norra sidan vägen</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Åsa Tengström</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Åsa Tengström, Anna Ljunggren</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 2562-2025 artfynd.xlsx
+++ b/artfynd/A 2562-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2361934</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2361935</t>
         </is>
       </c>
     </row>
@@ -1001,6 +1016,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86493913</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1127,6 +1147,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125657936</t>
         </is>
       </c>
     </row>
@@ -1245,6 +1270,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86493916</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1361,6 +1391,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86493935</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1481,8 +1516,22 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125657779</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>